--- a/Data/Regression Evidence 2025/Workday_NewHire_Slovakia_Regression_PK17.xlsx
+++ b/Data/Regression Evidence 2025/Workday_NewHire_Slovakia_Regression_PK17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{B0A6869C-43F5-4F1A-B29E-69CFE32C2114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{1D03765F-1B84-4CED-BA90-2E926AA7C989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="136">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -250,7 +250,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10700259</t>
+    <t>10700459</t>
   </si>
   <si>
     <t>Passed</t>
@@ -262,10 +262,10 @@
     <t>Slovakia</t>
   </si>
   <si>
-    <t>Kyla</t>
-  </si>
-  <si>
-    <t>Lubowitz</t>
+    <t>Macie</t>
+  </si>
+  <si>
+    <t>Labadie</t>
   </si>
   <si>
     <t>041/562 66 84</t>
@@ -398,13 +398,19 @@
     <t>Test2</t>
   </si>
   <si>
+    <t>10700473</t>
+  </si>
+  <si>
     <t>870 Store Management (Wazup Zudimi (9581610))</t>
   </si>
   <si>
-    <t>Delphine</t>
-  </si>
-  <si>
-    <t>Auto 96270717</t>
+    <t>Hilma</t>
+  </si>
+  <si>
+    <t>Bruen</t>
+  </si>
+  <si>
+    <t>Auto 98919828</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -484,7 +490,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -505,14 +511,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -687,17 +698,17 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -712,7 +723,7 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -757,7 +768,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1439,7 +1450,7 @@
       </c>
       <c r="W2" s="21">
         <f t="shared" ref="W2:W3" ca="1" si="0">TODAY()-31</f>
-        <v>45824</v>
+        <v>45846</v>
       </c>
       <c r="X2" s="18" t="s">
         <v>87</v>
@@ -1476,7 +1487,7 @@
       </c>
       <c r="AI2" s="21">
         <f ca="1">TODAY()+365</f>
-        <v>46220</v>
+        <v>46242</v>
       </c>
       <c r="AJ2" s="18" t="s">
         <v>96</v>
@@ -1531,7 +1542,7 @@
       </c>
       <c r="BA2" s="19">
         <f t="shared" ref="BA2:BA3" ca="1" si="1">TODAY()+90</f>
-        <v>45945</v>
+        <v>45967</v>
       </c>
       <c r="BB2" s="15" t="s">
         <v>106</v>
@@ -1547,15 +1558,15 @@
       </c>
       <c r="BF2" s="19">
         <f t="shared" ref="BF2:BF3" ca="1" si="2">W2</f>
-        <v>45824</v>
+        <v>45846</v>
       </c>
       <c r="BG2" s="19">
         <f t="shared" ref="BG2:BG3" ca="1" si="3">W2</f>
-        <v>45824</v>
+        <v>45846</v>
       </c>
       <c r="BH2" s="21">
         <f t="shared" ref="BH2:BH3" ca="1" si="4">AI2</f>
-        <v>46220</v>
+        <v>46242</v>
       </c>
       <c r="BI2" s="28" t="s">
         <v>76</v>
@@ -1565,7 +1576,7 @@
       </c>
       <c r="BK2" s="30">
         <f t="array" aca="1" ref="BK2:BK3" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>627374172</v>
+        <v>681487681</v>
       </c>
       <c r="BL2" s="31" t="s">
         <v>111</v>
@@ -1619,23 +1630,23 @@
       <c r="A3" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="13">
-        <v>10700286</v>
+      <c r="B3" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="C3" s="35" t="s">
         <v>74</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>76</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="H3" s="15" t="s">
         <v>79</v>
@@ -1684,25 +1695,25 @@
       </c>
       <c r="W3" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>45824</v>
+        <v>45846</v>
       </c>
       <c r="X3" s="18" t="s">
         <v>87</v>
       </c>
       <c r="Y3" s="22" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Z3" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AA3" s="24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AB3" s="19" t="s">
         <v>91</v>
       </c>
       <c r="AC3" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AD3" s="15" t="s">
         <v>92</v>
@@ -1726,10 +1737,10 @@
         <v>96</v>
       </c>
       <c r="AK3" s="25" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AL3" s="25" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM3" s="18" t="s">
         <v>99</v>
@@ -1738,10 +1749,10 @@
         <v>100</v>
       </c>
       <c r="AO3" s="24" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AP3" s="26" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AQ3" s="15" t="s">
         <v>88</v>
@@ -1775,7 +1786,7 @@
       </c>
       <c r="BA3" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>45945</v>
+        <v>45967</v>
       </c>
       <c r="BB3" s="15" t="s">
         <v>106</v>
@@ -1784,18 +1795,18 @@
         <v>107</v>
       </c>
       <c r="BD3" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BE3" s="18" t="s">
         <v>109</v>
       </c>
       <c r="BF3" s="19">
         <f t="shared" ca="1" si="2"/>
-        <v>45824</v>
+        <v>45846</v>
       </c>
       <c r="BG3" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>45824</v>
+        <v>45846</v>
       </c>
       <c r="BH3" s="21" t="str">
         <f t="shared" si="4"/>
@@ -1809,10 +1820,10 @@
       </c>
       <c r="BK3" s="30">
         <f ca="1"/>
-        <v>379704720</v>
+        <v>389658341</v>
       </c>
       <c r="BL3" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="BM3" s="19" t="s">
         <v>112</v>
